--- a/CIEH_Extraction/data/output/cieh_verified.xlsx
+++ b/CIEH_Extraction/data/output/cieh_verified.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verified Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Verified Data'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Verified Data'!$A$1:$L$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,9 +57,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -504,8 +507,400 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>c6ee74b227ddd807e214b2edc7b8389614e22d24673cb3e6af09a0251d0fb6f5-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Bristol City Council</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Response some not held.pdf</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>combined_premises_and_practitioners</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>new_registrations</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>During each of the financial years the following numbers of applicants were registered by this authority | Financial year Commencing 1 April: 2016 | S.15 Piercing Registration .- Tattooing PERS &amp; PREM: 7</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Table 'During each of the financial years...', Row '2016', Column 'S.15 Piercing Registration .- Tattooing PERS &amp; PREM'</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>sriram</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>c6ee74b227ddd807e214b2edc7b8389614e22d24673cb3e6af09a0251d0fb6f5-0002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Bristol City Council</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Response some not held.pdf</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>tattoo_practitioners</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>new_registrations</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>During each of the financial years the following numbers of applicants were registered by this authority | Financial year Commencing 1 April: 2016 | S.15 Piercing Registration. Tattooing -PERSON: 7</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Table 'During each of the financial years...', Row '2016', Column 'S.15 Piercing Registration. Tattooing -PERSON'</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>sriram</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>c6ee74b227ddd807e214b2edc7b8389614e22d24673cb3e6af09a0251d0fb6f5-0003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Bristol City Council</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Response some not held.pdf</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>combined_premises_and_practitioners</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>new_registrations</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>During each of the financial years the following numbers of applicants were registered by this authority | Financial year Commencing 1 April: 2017 | S.15 Piercing Registration .- Tattooing PERS &amp; PREM: 9</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Table 'During each of the financial years...', Row '2017', Column 'S.15 Piercing Registration .- Tattooing PERS &amp; PREM'</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>sriram</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>c6ee74b227ddd807e214b2edc7b8389614e22d24673cb3e6af09a0251d0fb6f5-0004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Bristol City Council</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Response some not held.pdf</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>tattoo_practitioners</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>new_registrations</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>During each of the financial years the following numbers of applicants were registered by this authority | Financial year Commencing 1 April: 2017 | S.15 Piercing Registration. Tattooing -PERSON: 21</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Table 'During each of the financial years...', Row '2017', Column 'S.15 Piercing Registration. Tattooing -PERSON'</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>sriram</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>c6ee74b227ddd807e214b2edc7b8389614e22d24673cb3e6af09a0251d0fb6f5-0005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Bristol City Council</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Response some not held.pdf</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>tattoo_premises</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>new_registrations</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>During each of the financial years the following numbers of applicants were registered by this authority | Financial year Commencing 1 April: 2017 | S.15 Piercing Registration.- Tattooing PREMISES: 5</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Table 'During each of the financial years...', Row '2017', Column 'S.15 Piercing Registration.- Tattooing PREMISES'</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>sriram</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>c6ee74b227ddd807e214b2edc7b8389614e22d24673cb3e6af09a0251d0fb6f5-0006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Bristol City Council</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Response some not held.pdf</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>combined_premises_and_practitioners</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>new_registrations</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>During each of the financial years the following numbers of applicants were registered by this authority | Financial year Commencing 1 April: 2018 | S.15 Piercing Registration .- Tattooing PERS &amp; PREM: 5</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Table 'During each of the financial years...', Row '2018', Column 'S.15 Piercing Registration .- Tattooing PERS &amp; PREM'</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>sriram</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>c6ee74b227ddd807e214b2edc7b8389614e22d24673cb3e6af09a0251d0fb6f5-0007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Bristol City Council</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Response some not held.pdf</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>tattoo_practitioners</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>new_registrations</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>During each of the financial years the following numbers of applicants were registered by this authority | Financial year Commencing 1 April: 2018 | S.15 Piercing Registration. Tattooing -PERSON: 27</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Table 'During each of the financial years...', Row '2018', Column 'S.15 Piercing Registration. Tattooing -PERSON'</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>sriram</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>